--- a/Design/Excel/ET/Datas/Game/UIEntity.xlsx
+++ b/Design/Excel/ET/Datas/Game/UIEntity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8018D0EF-28E2-4D45-B667-38462CA2CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C977EEDE-11EF-4E28-A267-7E759C2704A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -83,13 +83,6 @@
   </si>
   <si>
     <t>UI</t>
-  </si>
-  <si>
-    <t>UIHeadItem</t>
-  </si>
-  <si>
-    <t>UIHeadItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -539,23 +532,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Excel/ET/Datas/Game/UIEntity.xlsx
+++ b/Design/Excel/ET/Datas/Game/UIEntity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C977EEDE-11EF-4E28-A267-7E759C2704A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100863DB-F565-43E3-BC02-D03ECF54EBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -83,13 +83,21 @@
   </si>
   <si>
     <t>UI</t>
+  </si>
+  <si>
+    <t>Map0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +108,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -124,9 +140,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -433,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -532,6 +551,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Excel/ET/Datas/Game/UIEntity.xlsx
+++ b/Design/Excel/ET/Datas/Game/UIEntity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100863DB-F565-43E3-BC02-D03ECF54EBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E9F380-BCFC-4C13-8E6E-D6865A712E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -90,6 +90,14 @@
   </si>
   <si>
     <t>Map1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WidgetTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -452,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
@@ -538,8 +546,8 @@
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -582,6 +590,23 @@
         <v>20</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
         <v>0</v>
       </c>
     </row>
